--- a/output/pdf_financials_xlsx/CGX.xlsx
+++ b/output/pdf_financials_xlsx/CGX.xlsx
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1113.284</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1398.406</v>
+        <v>98.64</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>112.881</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>25.707</v>
       </c>
     </row>
     <row r="11">
@@ -860,16 +860,16 @@
         <v>656.669</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-10.403</v>
+        <v>1008.451</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-48.231</v>
+        <v>1251.535</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1274.756</v>
+        <v>1161.875</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1284.766</v>
+        <v>1259.059</v>
       </c>
     </row>
     <row r="12">
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.307</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.186</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.204</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.222</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.274</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.252</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.897</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>1.356</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="13">
@@ -1620,40 +1620,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>116.534</v>
+        <v>116.841</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>97.41500000000001</v>
+        <v>97.745</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>171.168</v>
+        <v>171.354</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>109.318</v>
+        <v>109.522</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>97.836</v>
+        <v>98.05800000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>97.54600000000001</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>77.176</v>
+        <v>77.428</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-245.383</v>
+        <v>-245.151</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.31</v>
+        <v>0.413</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>136.646</v>
+        <v>135.29</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-44.107</v>
+        <v>-44.977</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-37.233</v>
+        <v>-37.397</v>
       </c>
     </row>
     <row r="28">
@@ -1706,28 +1706,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>187.424</v>
+        <v>187.731</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>174.865</v>
+        <v>175.195</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>260.507</v>
+        <v>260.693</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>215.259</v>
+        <v>215.463</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>217.752</v>
+        <v>217.974</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>229.398</v>
+        <v>229.672</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>77.176</v>
+        <v>77.428</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-245.383</v>
+        <v>-245.151</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>220.168</v>
@@ -1749,28 +1749,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>16.00181683595628</v>
+        <v>16.02802776822023</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>14.16236608256474</v>
+        <v>14.18909287641854</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>19.00202998957652</v>
+        <v>19.01559729324998</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>14.56099669491032</v>
+        <v>14.57479608692535</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>14.00274071792405</v>
+        <v>14.01701663015163</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>14.22677957229983</v>
+        <v>14.24377247373232</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.634788781284044</v>
+        <v>4.649922589370541</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-37.3678367640318</v>
+        <v>-37.33250694033067</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>19.96298784728361</v>
@@ -44640,7 +44640,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -49184,7 +49184,7 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -55072,7 +55072,7 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -59396,7 +59396,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -61356,7 +61356,7 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E748" s="5" t="n">
@@ -63272,7 +63272,7 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
@@ -65652,7 +65652,7 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E807" s="5" t="n">

--- a/output/pdf_financials_xlsx/CGX.xlsx
+++ b/output/pdf_financials_xlsx/CGX.xlsx
@@ -1681,22 +1681,22 @@
         <v>131.852</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>145.946</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>102.247</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>93.512</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>85.566</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>83.962</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>81.896</v>
       </c>
     </row>
     <row r="29">
@@ -1724,10 +1724,10 @@
         <v>229.672</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>77.428</v>
+        <v>223.374</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-245.151</v>
+        <v>-142.904</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>220.168</v>
@@ -1767,10 +1767,10 @@
         <v>14.24377247373232</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.649922589370541</v>
+        <v>13.41467955362473</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-37.33250694033067</v>
+        <v>-21.76195313011578</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>19.96298784728361</v>
@@ -4859,16 +4859,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>145.946</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>102.247</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>93.512</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>87.657</v>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
@@ -27024,7 +27024,11 @@
           <t>Depreciation - right-of-use assets</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -31698,7 +31702,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -39684,7 +39692,11 @@
           <t>Depreciation - right-of-use assets</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -60846,7 +60858,11 @@
           <t>Depreciation - right-of-use assets</t>
         </is>
       </c>
-      <c r="D741" t="inlineStr"/>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E741" t="inlineStr">
         <is>
           <t>-</t>
@@ -62752,7 +62768,11 @@
           <t>Depreciation - right-of-use assets</t>
         </is>
       </c>
-      <c r="D768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E768" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CGX.xlsx
+++ b/output/pdf_financials_xlsx/CGX.xlsx
@@ -1298,13 +1298,13 @@
         <v>-9.679</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>138.051</v>
+        <v>-130.785</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-105.684</v>
+        <v>-104.162</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-37.233</v>
+        <v>-36.924</v>
       </c>
     </row>
     <row r="21">
@@ -2155,42 +2155,40 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>15.797</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>19.557</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>18.558</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>23.196</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>27.227</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>20.613</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>31.418</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>27.353</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>22.868</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>12.616</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.089</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>26.151</v>
       </c>
     </row>
     <row r="41">
@@ -2200,37 +2198,37 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>100.891</v>
+        <v>116.688</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>19.936</v>
+        <v>39.493</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>121.398</v>
+        <v>139.956</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>115.903</v>
+        <v>139.099</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>115.903</v>
+        <v>143.13</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>165.586</v>
+        <v>186.199</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>168.065</v>
+        <v>199.483</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>80.679</v>
+        <v>108.032</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>107.088</v>
+        <v>129.956</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>18.844</v>
+        <v>31.46</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>97.68899999999999</v>
+        <v>118.778</v>
       </c>
       <c r="M41" s="1" t="inlineStr">
         <is>
@@ -2515,37 +2513,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.838</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.923</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10.025</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>11.319</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>11.319</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>20.263</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>31.578</v>
+        <v>0.16</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>15.349</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>26.685</v>
+        <v>3.817</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>110.786</v>
+        <v>89.697</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -2897,42 +2895,40 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>1026.233</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>1121.215</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>1226.258</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>1343.558</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>1507.195</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>1616.481</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>1730.233</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>1696.692</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>1753.994</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>1689.511</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1756.179</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>1638.042</v>
       </c>
     </row>
     <row r="57">
@@ -2942,42 +2938,40 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>567.121</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>625.683</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>693.066</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>778.679</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>879.066</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>982.127</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>1067.435</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>1232.253</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>1304.499</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>1295.129</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1357.064</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>1287.761</v>
       </c>
     </row>
     <row r="58">
@@ -2987,22 +2981,22 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0</v>
+        <v>459.112</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0</v>
+        <v>495.532</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
+        <v>533.192</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>564.879</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0</v>
+        <v>628.129</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>634.354</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>1232.849</v>
@@ -3122,22 +3116,22 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>680.301</v>
+        <v>221.189</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>761.824</v>
+        <v>228.632</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>789.2</v>
+        <v>224.321</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>789.2</v>
+        <v>161.071</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>930.456</v>
+        <v>296.102</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>962.4059999999999</v>
@@ -3542,19 +3536,19 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>3.058</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>106.352</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>101.058</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>96.093</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>85.03</v>
       </c>
       <c r="L70" s="3" t="n">
         <v>0</v>
@@ -3587,19 +3581,19 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>3.058</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>106.352</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>101.058</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>96.093</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>85.03</v>
       </c>
       <c r="L71" s="3" t="n">
         <v>0</v>
@@ -3767,19 +3761,19 @@
         <v>25.174</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>30.454</v>
+        <v>27.396</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>147.398</v>
+        <v>41.046</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>404.272</v>
+        <v>303.214</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>320.356</v>
+        <v>224.263</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>418.125</v>
+        <v>333.095</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>0</v>
@@ -3902,22 +3896,22 @@
         <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>10.789</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>1261.243</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>1004.465</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>1004.546</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>17.101</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>993.404</v>
       </c>
       <c r="M78" s="1" t="inlineStr">
         <is>
@@ -3947,22 +3941,22 @@
         <v>298.472</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>580</v>
+        <v>590.789</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>625</v>
+        <v>1886.243</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>739.211</v>
+        <v>1743.676</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>824.888</v>
+        <v>1829.434</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>-80.971</v>
+        <v>-63.87</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>817.439</v>
+        <v>1810.843</v>
       </c>
       <c r="M79" s="1" t="inlineStr">
         <is>
@@ -3992,22 +3986,22 @@
         <v>0.3985035688441111</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.854183511018231</v>
+        <v>0.8745764059786955</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1.057540347279329</v>
+        <v>3.371599373259289</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-3.36428594184496</v>
+        <v>-8.395725527140991</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>-3.894397915151973</v>
+        <v>-9.090650287516405</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>-5.116650868878357</v>
+        <v>1.337124802527646</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.3598687558661884</v>
+        <v>0.7972042164357172</v>
       </c>
       <c r="M80" s="1" t="inlineStr">
         <is>
@@ -4217,22 +4211,22 @@
         <v>275.693</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>166.561</v>
+        <v>155.772</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>1293.834</v>
+        <v>32.591</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>1033.128</v>
+        <v>28.663</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>1021.728</v>
+        <v>17.182</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>97.06100000000001</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>1493.488</v>
+        <v>500.084</v>
       </c>
       <c r="M85" s="1" t="inlineStr">
         <is>
@@ -4820,10 +4814,10 @@
         <v>-248.722</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-9.679</v>
+        <v>0.113</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>138.051</v>
+        <v>167.164</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-37.681</v>
@@ -5458,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0</v>
+        <v>-7.447</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>0</v>
@@ -8536,7 +8530,11 @@
           <t>Lease obligations 1,010,505</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11824,7 +11822,11 @@
           <t>Lease obligations 14</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -12192,7 +12194,11 @@
           <t>Lease obligations 14</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -13976,7 +13982,11 @@
           <t>Lease obligations (note 14)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -14354,7 +14364,11 @@
           <t>Lease obligations (note 14)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -16018,7 +16032,11 @@
           <t>Lease obligations (notes 16 and 31)</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -16458,7 +16476,11 @@
           <t>Lease obligations (notes 16 and 31)</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -26874,11 +26896,7 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -30380,7 +30398,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -37922,7 +37944,11 @@
           <t>Gain on acquisition of business</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -39978,7 +40004,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -40025,7 +40055,7 @@
         </is>
       </c>
       <c r="N452" s="5" t="n">
-        <v>130.785</v>
+        <v>-130.785</v>
       </c>
       <c r="O452" s="5" t="n">
         <v>-104.162</v>
